--- a/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
+++ b/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.2.0</t>
+    <t>2026.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:53:17+00:00</t>
+    <t>2026-06-14T20:00:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
+++ b/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.4.0</t>
+    <t>2026.4.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-14T20:00:22+00:00</t>
+    <t>2026-06-15T12:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
+++ b/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:52:47+00:00</t>
+    <t>2026-07-07T06:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
+++ b/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.4.1</t>
+    <t>2026.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T06:23:56+00:00</t>
+    <t>2026-07-07T13:30:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
+++ b/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T13:30:17+00:00</t>
+    <t>2026-07-07T13:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
+++ b/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T13:37:50+00:00</t>
+    <t>2026-07-07T13:59:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
+++ b/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.5.0</t>
+    <t>2026.5.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T13:59:08+00:00</t>
+    <t>2026-07-27T21:31:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
+++ b/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.5.2</t>
+    <t>2026.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T21:31:58+00:00</t>
+    <t>2026-09-02T06:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
+++ b/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.6.0</t>
+    <t>2026.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:53+00:00</t>
+    <t>2026-09-02T06:41:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
+++ b/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:55+00:00</t>
+    <t>2026-09-02T06:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
+++ b/dev/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-4pt.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:47:03+00:00</t>
+    <t>2026-09-02T07:20:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
